--- a/output/pdf_financials_xlsx/NXLV.xlsx
+++ b/output/pdf_financials_xlsx/NXLV.xlsx
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007284</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.014889</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00068</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1011,16 +1011,16 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.084422</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.02575</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.177211</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.042033</v>
       </c>
     </row>
     <row r="13">
@@ -1803,13 +1803,13 @@
         <v>-0.01828</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.517274</v>
+        <v>-0.524558</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.93356</v>
+        <v>-4.948449</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.19124</v>
+        <v>-0.19192</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.338876</v>
@@ -1832,16 +1832,16 @@
         <v>9.404367000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>8.113187999999999</v>
+        <v>8.028765999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.903803</v>
+        <v>-1.929553</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>15.913234</v>
+        <v>15.736023</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.998361</v>
+        <v>6.956328</v>
       </c>
     </row>
     <row r="28">
@@ -1905,13 +1905,13 @@
         <v>-0.01828</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.517274</v>
+        <v>-0.524558</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.93356</v>
+        <v>-4.948449</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.19124</v>
+        <v>-0.19192</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.338876</v>
@@ -1934,16 +1934,16 @@
         <v>9.404367000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.113187999999999</v>
+        <v>8.028765999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.903803</v>
+        <v>-1.929553</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>15.913234</v>
+        <v>15.736023</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6.998361</v>
+        <v>6.956328</v>
       </c>
     </row>
     <row r="30">
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.104659</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
@@ -2194,19 +2194,19 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>17.695837</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.813765</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.340476</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.498773999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.390027</v>
       </c>
     </row>
     <row r="35">
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.104659</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
@@ -2296,19 +2296,19 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>17.695837</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.813765</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.340476</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.498773999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.390027</v>
       </c>
     </row>
     <row r="37">
@@ -2900,7 +2900,7 @@
         <v>0.01</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.148409</v>
+        <v>0.04375</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -2908,19 +2908,19 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>18.507151</v>
+        <v>0.811314</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.057018</v>
+        <v>1.243253</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.428831</v>
+        <v>1.088355</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.528629</v>
+        <v>1.029855</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.337051000000001</v>
+        <v>5.947024</v>
       </c>
     </row>
     <row r="49">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -30520,7 +30520,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -31532,7 +31532,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -36546,7 +36546,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">

--- a/output/pdf_financials_xlsx/NXLV.xlsx
+++ b/output/pdf_financials_xlsx/NXLV.xlsx
@@ -1255,7 +1255,7 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.236</v>
+        <v>-0.236</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.018803</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
@@ -1880,19 +1880,19 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.337753</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.478602</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.410708</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.598629</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.5327499999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1923,7 +1923,7 @@
         <v>-0.324418</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.927936</v>
+        <v>-0.909133</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1931,19 +1931,19 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>9.404367000000001</v>
+        <v>9.74212</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.028765999999999</v>
+        <v>8.507368</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.929553</v>
+        <v>-1.518845</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>15.736023</v>
+        <v>16.334652</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6.956328</v>
+        <v>7.489078</v>
       </c>
     </row>
     <row r="30">
@@ -3773,48 +3773,46 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.01309</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.045855</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.06669799999999999</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.090961</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.02658</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.186707</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.252135</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.273298</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.223869</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.263233</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.917293</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.50625</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>1.415528</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>1.565816</v>
       </c>
     </row>
     <row r="65">
@@ -3926,48 +3924,46 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0191</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11701</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.174593</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.445259</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.362591</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.801534</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.862056</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.12423</v>
       </c>
     </row>
     <row r="68">
@@ -5768,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.018803</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
@@ -5776,19 +5772,19 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.337753</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.478602</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.410708</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.598629</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.5327499999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6278,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.07434300000000001</v>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
@@ -6286,19 +6282,19 @@
         </is>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>1.055225</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.310315</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.4616</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>1.411801</v>
       </c>
     </row>
     <row r="111">
@@ -7629,7 +7625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R359"/>
+  <dimension ref="A1:R365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18298,7 +18294,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -18374,7 +18374,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -18622,7 +18626,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -23220,7 +23228,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -24939,10 +24951,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E207" s="5" t="n">
+        <v>0.019443</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -29435,24 +29445,26 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Rental income</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>-0.01828</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29484,55 +29496,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L260" s="5" t="n">
-        <v>0.157492</v>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N260" s="5" t="n">
-        <v>7.525715</v>
-      </c>
-      <c r="O260" s="5" t="n">
-        <v>11.864526</v>
-      </c>
-      <c r="P260" s="5" t="n">
-        <v>18.475666</v>
-      </c>
-      <c r="Q260" s="5" t="n">
-        <v>24.034078</v>
-      </c>
-      <c r="R260" s="5" t="n">
-        <v>34.555237</v>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Property operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in sales tax recoverable</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" s="5" t="n">
+        <v>-0.001163</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29564,55 +29582,65 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L261" s="5" t="n">
-        <v>0.060567</v>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N261" s="5" t="n">
-        <v>3.274706</v>
-      </c>
-      <c r="O261" s="5" t="n">
-        <v>5.194082</v>
-      </c>
-      <c r="P261" s="5" t="n">
-        <v>7.43915</v>
-      </c>
-      <c r="Q261" s="5" t="n">
-        <v>9.769425</v>
-      </c>
-      <c r="R261" s="5" t="n">
-        <v>13.872141</v>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Property operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Net property operating income</t>
+          <t>Proceeds from issuance of shares</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="n">
+        <v>0.0001</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29644,55 +29672,65 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L262" s="5" t="n">
-        <v>0.096925</v>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N262" s="5" t="n">
-        <v>4.251009</v>
-      </c>
-      <c r="O262" s="5" t="n">
-        <v>6.670444</v>
-      </c>
-      <c r="P262" s="5" t="n">
-        <v>11.036516</v>
-      </c>
-      <c r="Q262" s="5" t="n">
-        <v>14.264653</v>
-      </c>
-      <c r="R262" s="5" t="n">
-        <v>20.683096</v>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Net change in cash and Cash – End of period</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="n">
+        <v>0.0001</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29744,14 +29782,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P263" s="5" t="n">
-        <v>-1.554492</v>
-      </c>
-      <c r="Q263" s="5" t="n">
-        <v>-1.760571</v>
-      </c>
-      <c r="R263" s="5" t="n">
-        <v>-2.273772</v>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -29762,12 +29806,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 10)</t>
+          <t>Rental income</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -29806,36 +29850,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L264" s="5" t="n">
+        <v>0.157492</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N264" s="5" t="n">
+        <v>7.525715</v>
+      </c>
+      <c r="O264" s="5" t="n">
+        <v>11.864526</v>
+      </c>
+      <c r="P264" s="5" t="n">
+        <v>18.475666</v>
       </c>
       <c r="Q264" s="5" t="n">
-        <v>-0.4542</v>
+        <v>24.034078</v>
       </c>
       <c r="R264" s="5" t="n">
-        <v>-0.4809</v>
+        <v>34.555237</v>
       </c>
     </row>
     <row r="265">
@@ -29846,12 +29882,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Property operating expenses</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -29894,34 +29930,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L265" s="5" t="n">
+        <v>0.060567</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N265" s="5" t="n">
+        <v>3.274706</v>
+      </c>
+      <c r="O265" s="5" t="n">
+        <v>5.194082</v>
       </c>
       <c r="P265" s="5" t="n">
-        <v>1.858092</v>
+        <v>7.43915</v>
       </c>
       <c r="Q265" s="5" t="n">
-        <v>2.214771</v>
+        <v>9.769425</v>
       </c>
       <c r="R265" s="5" t="n">
-        <v>2.754672</v>
+        <v>13.872141</v>
       </c>
     </row>
     <row r="266">
@@ -29932,17 +29962,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Property operating expenses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Net property operating income</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -29981,7 +30011,7 @@
         </is>
       </c>
       <c r="L266" s="5" t="n">
-        <v>0.103302</v>
+        <v>0.096925</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
@@ -29989,19 +30019,19 @@
         </is>
       </c>
       <c r="N266" s="5" t="n">
-        <v>-1.768777</v>
+        <v>4.251009</v>
       </c>
       <c r="O266" s="5" t="n">
-        <v>-2.593905</v>
+        <v>6.670444</v>
       </c>
       <c r="P266" s="5" t="n">
-        <v>-5.955579</v>
+        <v>11.036516</v>
       </c>
       <c r="Q266" s="5" t="n">
-        <v>-7.706445</v>
+        <v>14.264653</v>
       </c>
       <c r="R266" s="5" t="n">
-        <v>-10.030925</v>
+        <v>20.683096</v>
       </c>
     </row>
     <row r="267">
@@ -30012,15 +30042,19 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Amortization of finance costs (note 9)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -30076,16 +30110,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P267" s="5" t="n">
+        <v>-1.554492</v>
       </c>
       <c r="Q267" s="5" t="n">
-        <v>-0.598629</v>
+        <v>-1.760571</v>
       </c>
       <c r="R267" s="5" t="n">
-        <v>-0.5327499999999999</v>
+        <v>-2.273772</v>
       </c>
     </row>
     <row r="268">
@@ -30096,12 +30128,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Accretion expense (note 9)</t>
+          <t>Stock-based compensation (note 10)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -30166,10 +30198,10 @@
         </is>
       </c>
       <c r="Q268" s="5" t="n">
-        <v>-0.4616</v>
+        <v>-0.4542</v>
       </c>
       <c r="R268" s="5" t="n">
-        <v>-1.411801</v>
+        <v>-0.4809</v>
       </c>
     </row>
     <row r="269">
@@ -30180,15 +30212,19 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Finance costs total</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -30224,28 +30260,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L269" s="5" t="n">
-        <v>0.196448</v>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N269" s="5" t="n">
-        <v>-3.249755</v>
-      </c>
-      <c r="O269" s="5" t="n">
-        <v>-3.382822</v>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P269" s="5" t="n">
-        <v>-6.366287</v>
+        <v>1.858092</v>
       </c>
       <c r="Q269" s="5" t="n">
-        <v>-8.766674</v>
+        <v>2.214771</v>
       </c>
       <c r="R269" s="5" t="n">
-        <v>-11.975476</v>
+        <v>2.754672</v>
       </c>
     </row>
     <row r="270">
@@ -30256,15 +30298,19 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Fair value adjustments to investment properties (note 7)</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -30300,36 +30346,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L270" s="5" t="n">
+        <v>0.103302</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N270" s="5" t="n">
+        <v>-1.768777</v>
+      </c>
+      <c r="O270" s="5" t="n">
+        <v>-2.593905</v>
+      </c>
+      <c r="P270" s="5" t="n">
+        <v>-5.955579</v>
       </c>
       <c r="Q270" s="5" t="n">
-        <v>12.337616</v>
+        <v>-7.706445</v>
       </c>
       <c r="R270" s="5" t="n">
-        <v>0.7951780000000001</v>
+        <v>-10.030925</v>
       </c>
     </row>
     <row r="271">
@@ -30340,12 +30378,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Gain on sale of investment properties (note 7)</t>
+          <t>Amortization of finance costs (note 9)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -30410,10 +30448,10 @@
         </is>
       </c>
       <c r="Q271" s="5" t="n">
-        <v>0.115199</v>
+        <v>-0.598629</v>
       </c>
       <c r="R271" s="5" t="n">
-        <v>0.078032</v>
+        <v>-0.5327499999999999</v>
       </c>
     </row>
     <row r="272">
@@ -30424,12 +30462,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Income from equity-accounted investment (note 6)</t>
+          <t>Accretion expense (note 9)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -30493,13 +30531,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q272" s="5" t="n">
+        <v>-0.4616</v>
       </c>
       <c r="R272" s="5" t="n">
-        <v>0.13017</v>
+        <v>-1.411801</v>
       </c>
     </row>
     <row r="273">
@@ -30510,32 +30546,34 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Finance costs total</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F273" s="5" t="n">
-        <v>0.007284</v>
-      </c>
-      <c r="G273" s="5" t="n">
-        <v>0.014889</v>
-      </c>
-      <c r="H273" s="5" t="n">
-        <v>0.00068</v>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -30552,34 +30590,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L273" s="5" t="n">
+        <v>0.196448</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N273" s="5" t="n">
+        <v>-3.249755</v>
       </c>
       <c r="O273" s="5" t="n">
-        <v>0.084422</v>
-      </c>
-      <c r="P273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.382822</v>
+      </c>
+      <c r="P273" s="5" t="n">
+        <v>-6.366287</v>
       </c>
       <c r="Q273" s="5" t="n">
-        <v>0.177211</v>
+        <v>-8.766674</v>
       </c>
       <c r="R273" s="5" t="n">
-        <v>0.042033</v>
+        <v>-11.975476</v>
       </c>
     </row>
     <row r="274">
@@ -30595,7 +30627,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Other income total</t>
+          <t>Fair value adjustments to investment properties (note 7)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -30644,11 +30676,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N274" s="5" t="n">
-        <v>9.938278</v>
-      </c>
-      <c r="O274" s="5" t="n">
-        <v>6.648079</v>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -30656,10 +30692,10 @@
         </is>
       </c>
       <c r="Q274" s="5" t="n">
-        <v>12.630026</v>
+        <v>12.337616</v>
       </c>
       <c r="R274" s="5" t="n">
-        <v>1.045413</v>
+        <v>0.7951780000000001</v>
       </c>
     </row>
     <row r="275">
@@ -30675,14 +30711,10 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Net income before income taxes</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Gain on sale of investment properties (note 7)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -30728,11 +30760,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N275" s="5" t="n">
-        <v>9.404367000000001</v>
-      </c>
-      <c r="O275" s="5" t="n">
-        <v>8.113187999999999</v>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P275" t="inlineStr">
         <is>
@@ -30740,10 +30776,10 @@
         </is>
       </c>
       <c r="Q275" s="5" t="n">
-        <v>15.913234</v>
+        <v>0.115199</v>
       </c>
       <c r="R275" s="5" t="n">
-        <v>6.998361</v>
+        <v>0.078032</v>
       </c>
     </row>
     <row r="276">
@@ -30759,14 +30795,10 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Provision for income tax expense (note 11)</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Income from equity-accounted investment (note 6)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -30827,11 +30859,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q276" s="5" t="n">
-        <v>-2.5</v>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R276" s="5" t="n">
-        <v>-2.655</v>
+        <v>0.13017</v>
       </c>
     </row>
     <row r="277">
@@ -30847,12 +30881,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -30860,20 +30894,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F277" s="5" t="n">
+        <v>0.007284</v>
+      </c>
+      <c r="G277" s="5" t="n">
+        <v>0.014889</v>
+      </c>
+      <c r="H277" s="5" t="n">
+        <v>0.00068</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -30905,10 +30933,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O277" s="5" t="n">
+        <v>0.084422</v>
       </c>
       <c r="P277" t="inlineStr">
         <is>
@@ -30916,10 +30942,10 @@
         </is>
       </c>
       <c r="Q277" s="5" t="n">
-        <v>13.413234</v>
+        <v>0.177211</v>
       </c>
       <c r="R277" s="5" t="n">
-        <v>4.343361</v>
+        <v>0.042033</v>
       </c>
     </row>
     <row r="278">
@@ -30935,14 +30961,10 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Net income per share – basic (note 13)</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other income total</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -30989,10 +31011,10 @@
         </is>
       </c>
       <c r="N278" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>9.938278</v>
       </c>
       <c r="O278" s="5" t="n">
-        <v>3e-08</v>
+        <v>6.648079</v>
       </c>
       <c r="P278" t="inlineStr">
         <is>
@@ -31000,10 +31022,10 @@
         </is>
       </c>
       <c r="Q278" s="5" t="n">
-        <v>6e-07</v>
+        <v>12.630026</v>
       </c>
       <c r="R278" s="5" t="n">
-        <v>1.3e-07</v>
+        <v>1.045413</v>
       </c>
     </row>
     <row r="279">
@@ -31019,12 +31041,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Net income per share – diluted (note 13)</t>
+          <t>Net income before income taxes</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -31073,10 +31095,10 @@
         </is>
       </c>
       <c r="N279" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>9.404367000000001</v>
       </c>
       <c r="O279" s="5" t="n">
-        <v>3e-08</v>
+        <v>8.113187999999999</v>
       </c>
       <c r="P279" t="inlineStr">
         <is>
@@ -31084,10 +31106,10 @@
         </is>
       </c>
       <c r="Q279" s="5" t="n">
-        <v>6e-07</v>
+        <v>15.913234</v>
       </c>
       <c r="R279" s="5" t="n">
-        <v>1.3e-07</v>
+        <v>6.998361</v>
       </c>
     </row>
     <row r="280">
@@ -31098,15 +31120,19 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 8)</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Provision for income tax expense (note 11)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -31162,16 +31188,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P280" s="5" t="n">
-        <v>-0.3036</v>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q280" s="5" t="n">
-        <v>-0.4542</v>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.5</v>
+      </c>
+      <c r="R280" s="5" t="n">
+        <v>-2.655</v>
       </c>
     </row>
     <row r="281">
@@ -31182,15 +31208,19 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Amortization of finance costs (note 7)</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Net income and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -31246,16 +31276,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P281" s="5" t="n">
-        <v>-0.410708</v>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q281" s="5" t="n">
-        <v>-0.598629</v>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.413234</v>
+      </c>
+      <c r="R281" s="5" t="n">
+        <v>4.343361</v>
       </c>
     </row>
     <row r="282">
@@ -31266,15 +31296,19 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Accretion expense (note 7)</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Net income per share – basic (note 13)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -31320,15 +31354,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N282" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="O282" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="P282" t="inlineStr">
         <is>
@@ -31336,12 +31366,10 @@
         </is>
       </c>
       <c r="Q282" s="5" t="n">
-        <v>-0.4616</v>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6e-07</v>
+      </c>
+      <c r="R282" s="5" t="n">
+        <v>1.3e-07</v>
       </c>
     </row>
     <row r="283">
@@ -31352,15 +31380,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Other income (loss)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Fair value adjustments to investment properties (note 5)</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Net income per share – diluted (note 13)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -31406,26 +31438,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P283" s="5" t="n">
-        <v>-4.74169</v>
+      <c r="N283" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="O283" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>12.337616</v>
-      </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6e-07</v>
+      </c>
+      <c r="R283" s="5" t="n">
+        <v>1.3e-07</v>
       </c>
     </row>
     <row r="284">
@@ -31436,12 +31464,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Other income (loss)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Gain on sale of investment properties (note 5)</t>
+          <t>Stock-based compensation (note 8)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -31500,13 +31528,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P284" s="5" t="n">
+        <v>-0.3036</v>
       </c>
       <c r="Q284" s="5" t="n">
-        <v>0.115199</v>
+        <v>-0.4542</v>
       </c>
       <c r="R284" t="inlineStr">
         <is>
@@ -31522,19 +31548,15 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Other income (loss)</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Amortization of finance costs (note 7)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -31591,10 +31613,10 @@
         </is>
       </c>
       <c r="P285" s="5" t="n">
-        <v>0.02575</v>
+        <v>-0.410708</v>
       </c>
       <c r="Q285" s="5" t="n">
-        <v>0.177211</v>
+        <v>-0.598629</v>
       </c>
       <c r="R285" t="inlineStr">
         <is>
@@ -31610,12 +31632,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Other income (loss)</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Other income (loss) total</t>
+          <t>Accretion expense (note 7)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -31674,11 +31696,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P286" s="5" t="n">
-        <v>-4.71594</v>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q286" s="5" t="n">
-        <v>12.630026</v>
+        <v>-0.4616</v>
       </c>
       <c r="R286" t="inlineStr">
         <is>
@@ -31699,14 +31723,10 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Fair value adjustments to investment properties (note 5)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -31763,10 +31783,10 @@
         </is>
       </c>
       <c r="P287" s="5" t="n">
-        <v>-1.903803</v>
+        <v>-4.74169</v>
       </c>
       <c r="Q287" s="5" t="n">
-        <v>15.913234</v>
+        <v>12.337616</v>
       </c>
       <c r="R287" t="inlineStr">
         <is>
@@ -31787,14 +31807,10 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (note 9)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Gain on sale of investment properties (note 5)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -31850,11 +31866,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P288" s="5" t="n">
-        <v>-0.3</v>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q288" s="5" t="n">
-        <v>-2.5</v>
+        <v>0.115199</v>
       </c>
       <c r="R288" t="inlineStr">
         <is>
@@ -31875,12 +31893,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -31939,10 +31957,10 @@
         </is>
       </c>
       <c r="P289" s="5" t="n">
-        <v>-2.203803</v>
+        <v>0.02575</v>
       </c>
       <c r="Q289" s="5" t="n">
-        <v>13.413234</v>
+        <v>0.177211</v>
       </c>
       <c r="R289" t="inlineStr">
         <is>
@@ -31963,14 +31981,10 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Net income (loss) per share – basic (notes 2 and 11)</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other income (loss) total</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -32027,10 +32041,10 @@
         </is>
       </c>
       <c r="P290" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>-4.71594</v>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>6e-07</v>
+        <v>12.630026</v>
       </c>
       <c r="R290" t="inlineStr">
         <is>
@@ -32051,12 +32065,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Net income (loss) per share – diluted (notes 2 and 11)</t>
+          <t>Net income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -32115,10 +32129,10 @@
         </is>
       </c>
       <c r="P291" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>-1.903803</v>
       </c>
       <c r="Q291" s="5" t="n">
-        <v>6e-07</v>
+        <v>15.913234</v>
       </c>
       <c r="R291" t="inlineStr">
         <is>
@@ -32134,17 +32148,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income (loss)</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Management wages and consulting fees</t>
+          <t>Deferred income tax expense (note 9)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -32192,21 +32206,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N292" s="5" t="n">
-        <v>0.918648</v>
-      </c>
-      <c r="O292" s="5" t="n">
-        <v>1.032526</v>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P292" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Q292" s="5" t="n">
+        <v>-2.5</v>
       </c>
       <c r="R292" t="inlineStr">
         <is>
@@ -32222,15 +32236,19 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income (loss)</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Filing and other fees</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
+          <t>Net income (loss) and comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -32261,32 +32279,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K293" s="5" t="n">
-        <v>0.019929</v>
-      </c>
-      <c r="L293" s="5" t="n">
-        <v>0.033316</v>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N293" s="5" t="n">
-        <v>-0.050524</v>
-      </c>
-      <c r="O293" s="5" t="n">
-        <v>-0.081923</v>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" s="5" t="n">
+        <v>-2.203803</v>
+      </c>
+      <c r="Q293" s="5" t="n">
+        <v>13.413234</v>
       </c>
       <c r="R293" t="inlineStr">
         <is>
@@ -32302,17 +32324,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income (loss)</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Net income (loss) per share – basic (notes 2 and 11)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -32345,32 +32367,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K294" s="5" t="n">
-        <v>0.004955</v>
-      </c>
-      <c r="L294" s="5" t="n">
-        <v>0.013097</v>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N294" s="5" t="n">
-        <v>0.025954</v>
-      </c>
-      <c r="O294" s="5" t="n">
-        <v>0.038062</v>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P294" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="Q294" s="5" t="n">
+        <v>6e-07</v>
       </c>
       <c r="R294" t="inlineStr">
         <is>
@@ -32386,15 +32412,19 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income (loss)</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Office and other</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Net income (loss) per share – diluted (notes 2 and 11)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -32425,32 +32455,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K295" s="5" t="n">
-        <v>0.010985</v>
-      </c>
-      <c r="L295" s="5" t="n">
-        <v>0.032132</v>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N295" s="5" t="n">
-        <v>-0.114482</v>
-      </c>
-      <c r="O295" s="5" t="n">
-        <v>-0.109888</v>
-      </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P295" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="Q295" s="5" t="n">
+        <v>6e-07</v>
       </c>
       <c r="R295" t="inlineStr">
         <is>
@@ -32471,12 +32505,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Management wages and consulting fees</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -32509,11 +32543,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K296" s="5" t="n">
-        <v>0.053612</v>
-      </c>
-      <c r="L296" s="5" t="n">
-        <v>0.183694</v>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
@@ -32521,10 +32559,10 @@
         </is>
       </c>
       <c r="N296" s="5" t="n">
-        <v>-0.137457</v>
+        <v>0.918648</v>
       </c>
       <c r="O296" s="5" t="n">
-        <v>-0.225614</v>
+        <v>1.032526</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -32555,7 +32593,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 10)</t>
+          <t>Filing and other fees</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -32589,15 +32627,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K297" s="5" t="n">
+        <v>0.019929</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>0.033316</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
@@ -32605,10 +32639,10 @@
         </is>
       </c>
       <c r="N297" s="5" t="n">
-        <v>-0.2881</v>
+        <v>-0.050524</v>
       </c>
       <c r="O297" s="5" t="n">
-        <v>-0.3345</v>
+        <v>-0.081923</v>
       </c>
       <c r="P297" t="inlineStr">
         <is>
@@ -32639,12 +32673,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Administrative expenses total</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -32678,10 +32712,10 @@
         </is>
       </c>
       <c r="K298" s="5" t="n">
-        <v>0.324418</v>
+        <v>0.004955</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>0.7579360000000001</v>
+        <v>0.013097</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
@@ -32689,10 +32723,10 @@
         </is>
       </c>
       <c r="N298" s="5" t="n">
-        <v>1.535165</v>
+        <v>0.025954</v>
       </c>
       <c r="O298" s="5" t="n">
-        <v>1.822513</v>
+        <v>0.038062</v>
       </c>
       <c r="P298" t="inlineStr">
         <is>
@@ -32718,12 +32752,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Deferred financing costs amortization expense (notes 8 and 9)</t>
+          <t>Office and other</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -32757,15 +32791,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K299" s="5" t="n">
+        <v>0.010985</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>0.032132</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
@@ -32773,10 +32803,10 @@
         </is>
       </c>
       <c r="N299" s="5" t="n">
-        <v>-0.337753</v>
+        <v>-0.114482</v>
       </c>
       <c r="O299" s="5" t="n">
-        <v>-0.478602</v>
+        <v>-0.109888</v>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -32802,15 +32832,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Accretion expense (note 8)</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -32841,15 +32875,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K300" s="5" t="n">
+        <v>0.053612</v>
+      </c>
+      <c r="L300" s="5" t="n">
+        <v>0.183694</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
@@ -32857,10 +32887,10 @@
         </is>
       </c>
       <c r="N300" s="5" t="n">
-        <v>-1.055225</v>
+        <v>-0.137457</v>
       </c>
       <c r="O300" s="5" t="n">
-        <v>-0.310315</v>
+        <v>-0.225614</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
@@ -32886,12 +32916,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Loss on modification of convertible debentures</t>
+          <t>Stock-based compensation (note 10)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -32941,12 +32971,10 @@
         </is>
       </c>
       <c r="N301" s="5" t="n">
-        <v>-0.08799999999999999</v>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.2881</v>
+      </c>
+      <c r="O301" s="5" t="n">
+        <v>-0.3345</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
@@ -32972,15 +33000,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Fair value adjustment to investment properties (note 6)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Administrative expenses total</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -33011,15 +33043,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K302" s="5" t="n">
+        <v>0.324418</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>0.7579360000000001</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
@@ -33027,10 +33055,10 @@
         </is>
       </c>
       <c r="N302" s="5" t="n">
-        <v>9.937148000000001</v>
+        <v>1.535165</v>
       </c>
       <c r="O302" s="5" t="n">
-        <v>6.563657</v>
+        <v>1.822513</v>
       </c>
       <c r="P302" t="inlineStr">
         <is>
@@ -33056,15 +33084,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Gain on sale of investment properties</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Deferred financing costs amortization expense (notes 8 and 9)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -33111,12 +33143,10 @@
         </is>
       </c>
       <c r="N303" s="5" t="n">
-        <v>0.00113</v>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.337753</v>
+      </c>
+      <c r="O303" s="5" t="n">
+        <v>0.478602</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -33142,19 +33172,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Deferred income tax expense</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Accretion expense (note 8)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -33200,13 +33226,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N304" s="5" t="n">
+        <v>-1.055225</v>
       </c>
       <c r="O304" s="5" t="n">
-        <v>-0.6</v>
+        <v>-0.310315</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
@@ -33232,12 +33256,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income for the years</t>
+          <t>Loss on modification of convertible debentures</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -33287,10 +33311,12 @@
         </is>
       </c>
       <c r="N305" s="5" t="n">
-        <v>9.404367000000001</v>
-      </c>
-      <c r="O305" s="5" t="n">
-        <v>7.513188</v>
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
@@ -33316,19 +33342,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Fair value adjustment to investment properties (note 6)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -33359,26 +33381,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K306" s="5" t="n">
-        <v>0.174814</v>
-      </c>
-      <c r="L306" s="5" t="n">
-        <v>0.479461</v>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N306" s="5" t="n">
+        <v>9.937148000000001</v>
+      </c>
+      <c r="O306" s="5" t="n">
+        <v>6.563657</v>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -33404,19 +33426,15 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Gain on sale of investment properties</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -33447,21 +33465,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K307" s="5" t="n">
-        <v>0.018941</v>
-      </c>
-      <c r="L307" s="5" t="n">
-        <v>0.016236</v>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N307" s="5" t="n">
+        <v>0.00113</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -33492,15 +33512,19 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Write-down of sales tax recoverable</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>Deferred income tax expense</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -33531,8 +33555,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K308" s="5" t="n">
-        <v>0.041182</v>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -33549,10 +33575,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O308" s="5" t="n">
+        <v>-0.6</v>
       </c>
       <c r="P308" t="inlineStr">
         <is>
@@ -33578,12 +33602,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Amortization expense (notes 10, 11)</t>
+          <t>Net income and comprehensive income for the years</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -33622,23 +33646,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L309" s="5" t="n">
-        <v>0.018803</v>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N309" s="5" t="n">
+        <v>9.404367000000001</v>
+      </c>
+      <c r="O309" s="5" t="n">
+        <v>7.513188</v>
       </c>
       <c r="P309" t="inlineStr">
         <is>
@@ -33664,15 +33686,19 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Accretion expense (note 10)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -33703,13 +33729,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K310" s="5" t="n">
+        <v>0.174814</v>
       </c>
       <c r="L310" s="5" t="n">
-        <v>0.07434300000000001</v>
+        <v>0.479461</v>
       </c>
       <c r="M310" t="inlineStr">
         <is>
@@ -33750,15 +33774,19 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Depreciation expense (note 6)</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -33789,13 +33817,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K311" s="5" t="n">
+        <v>0.018941</v>
       </c>
       <c r="L311" s="5" t="n">
-        <v>0.049949</v>
+        <v>0.016236</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
@@ -33836,12 +33862,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Loss on settlement of Bridge</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Loans (note 8)</t>
+          <t>Write-down of sales tax recoverable</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -33875,13 +33901,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L312" s="5" t="n">
-        <v>0.18</v>
+      <c r="K312" s="5" t="n">
+        <v>0.041182</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
@@ -33922,15 +33948,19 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Amortization expense (notes 10, 11)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -33967,7 +33997,7 @@
         </is>
       </c>
       <c r="L313" s="5" t="n">
-        <v>-0.159472</v>
+        <v>0.018803</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
@@ -34008,12 +34038,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts total</t>
+          <t>Accretion expense (note 10)</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -34053,7 +34083,7 @@
         </is>
       </c>
       <c r="L314" s="5" t="n">
-        <v>0.020528</v>
+        <v>0.07434300000000001</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
@@ -34094,19 +34124,15 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Depreciation expense (note 6)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -34143,7 +34169,7 @@
         </is>
       </c>
       <c r="L315" s="5" t="n">
-        <v>-0.927936</v>
+        <v>0.049949</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
@@ -34184,12 +34210,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts</t>
+          <t>Loss on settlement of Bridge</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Loans (note 8)</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -34229,7 +34255,7 @@
         </is>
       </c>
       <c r="L316" s="5" t="n">
-        <v>0.236</v>
+        <v>0.18</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
@@ -34275,14 +34301,10 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -34313,11 +34335,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K317" s="5" t="n">
-        <v>-0.324418</v>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L317" s="5" t="n">
-        <v>-0.691936</v>
+        <v>-0.159472</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
@@ -34363,14 +34387,10 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts total</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -34401,11 +34421,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K318" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L318" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.020528</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
@@ -34446,23 +34468,33 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares –</t>
+          <t>Gain on settlement of accounts</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F319" s="5" t="n">
-        <v>36.385953</v>
-      </c>
-      <c r="G319" s="5" t="n">
-        <v>45.825404</v>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -34474,14 +34506,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J319" s="5" t="n">
-        <v>6.356388</v>
-      </c>
-      <c r="K319" s="5" t="n">
-        <v>9.781076000000001</v>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L319" s="5" t="n">
-        <v>15.101037</v>
+        <v>-0.927936</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
@@ -34522,17 +34558,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Gain on settlement of accounts</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -34540,30 +34576,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F320" s="5" t="n">
-        <v>0.104263</v>
-      </c>
-      <c r="G320" s="5" t="n">
-        <v>0.085636</v>
-      </c>
-      <c r="H320" s="5" t="n">
-        <v>0.033373</v>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J320" s="5" t="n">
-        <v>0.2169</v>
-      </c>
-      <c r="K320" s="5" t="n">
-        <v>0.174814</v>
-      </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" s="5" t="n">
+        <v>0.236</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
@@ -34604,15 +34648,19 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Gain on settlement of accounts</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Filing and other fees</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -34633,19 +34681,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I321" s="5" t="n">
-        <v>0.008976</v>
-      </c>
-      <c r="J321" s="5" t="n">
-        <v>0.024788</v>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K321" s="5" t="n">
-        <v>0.019929</v>
-      </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.324418</v>
+      </c>
+      <c r="L321" s="5" t="n">
+        <v>-0.691936</v>
       </c>
       <c r="M321" t="inlineStr">
         <is>
@@ -34686,17 +34736,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Gain on settlement of accounts</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -34704,28 +34754,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F322" s="5" t="n">
-        <v>0.014922</v>
-      </c>
-      <c r="G322" s="5" t="n">
-        <v>0.022585</v>
-      </c>
-      <c r="H322" s="5" t="n">
-        <v>0.01074</v>
-      </c>
-      <c r="I322" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J322" s="5" t="n">
-        <v>0.004638</v>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K322" s="5" t="n">
-        <v>0.004955</v>
-      </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="L322" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
@@ -34766,29 +34824,23 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average outstanding common shares –</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Office and other</t>
+          <t>Weighted average outstanding common shares – basic and diluted</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E323" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F323" s="5" t="n">
+        <v>36.385953</v>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>45.825404</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -34801,15 +34853,13 @@
         </is>
       </c>
       <c r="J323" s="5" t="n">
-        <v>0.015884</v>
+        <v>6.356388</v>
       </c>
       <c r="K323" s="5" t="n">
-        <v>0.010985</v>
-      </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.781076000000001</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>15.101037</v>
       </c>
       <c r="M323" t="inlineStr">
         <is>
@@ -34855,34 +34905,38 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E324" s="5" t="n">
-        <v>0.01828</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.039618</v>
+        <v>0.104263</v>
       </c>
       <c r="G324" s="5" t="n">
-        <v>0.026595</v>
+        <v>0.085636</v>
       </c>
       <c r="H324" s="5" t="n">
-        <v>0.016867</v>
-      </c>
-      <c r="I324" s="5" t="n">
-        <v>0.016662</v>
+        <v>0.033373</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J324" s="5" t="n">
-        <v>0.014943</v>
+        <v>0.2169</v>
       </c>
       <c r="K324" s="5" t="n">
-        <v>0.053612</v>
+        <v>0.174814</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -34933,40 +34987,38 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Filing and other fees</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F325" s="5" t="n">
-        <v>0.014062</v>
-      </c>
-      <c r="G325" s="5" t="n">
-        <v>0.00147</v>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I325" s="5" t="n">
+        <v>0.008976</v>
       </c>
       <c r="J325" s="5" t="n">
-        <v>0.010945</v>
+        <v>0.024788</v>
       </c>
       <c r="K325" s="5" t="n">
-        <v>0.018941</v>
+        <v>0.019929</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -35017,42 +35069,36 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Write-down of sales tax recoverable</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F326" s="5" t="n">
+        <v>0.014922</v>
+      </c>
+      <c r="G326" s="5" t="n">
+        <v>0.022585</v>
+      </c>
+      <c r="H326" s="5" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="I326" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J326" s="5" t="n">
+        <v>0.004638</v>
       </c>
       <c r="K326" s="5" t="n">
-        <v>0.041182</v>
+        <v>0.004955</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -35103,14 +35149,10 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Office and other</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -35137,10 +35179,10 @@
         </is>
       </c>
       <c r="J327" s="5" t="n">
-        <v>-0.288098</v>
+        <v>0.015884</v>
       </c>
       <c r="K327" s="5" t="n">
-        <v>-0.324418</v>
+        <v>0.010985</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -35191,44 +35233,34 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="F328" s="5" t="n">
+        <v>0.039618</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>0.026595</v>
+      </c>
+      <c r="H328" s="5" t="n">
+        <v>0.016867</v>
+      </c>
+      <c r="I328" s="5" t="n">
+        <v>0.016662</v>
       </c>
       <c r="J328" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.014943</v>
       </c>
       <c r="K328" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.053612</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -35279,12 +35311,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -35292,31 +35324,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H329" s="5" t="n">
-        <v>0.002597</v>
-      </c>
-      <c r="I329" s="5" t="n">
-        <v>0.01234</v>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F329" s="5" t="n">
+        <v>0.014062</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>0.00147</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" s="5" t="n">
+        <v>0.010945</v>
+      </c>
+      <c r="K329" s="5" t="n">
+        <v>0.018941</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -35367,7 +35395,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable (Note 8)</t>
+          <t>Write-down of sales tax recoverable</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -35391,18 +35419,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I330" s="5" t="n">
-        <v>-0.025</v>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K330" s="5" t="n">
+        <v>0.041182</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -35453,34 +35481,44 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F331" s="5" t="n">
-        <v>0.063712</v>
-      </c>
-      <c r="G331" s="5" t="n">
-        <v>0.06486500000000001</v>
-      </c>
-      <c r="H331" s="5" t="n">
-        <v>0.039697</v>
-      </c>
-      <c r="I331" s="5" t="n">
-        <v>0.02493</v>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J331" s="5" t="n">
-        <v>0.015884</v>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.288098</v>
+      </c>
+      <c r="K331" s="5" t="n">
+        <v>-0.324418</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -35531,36 +35569,42 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E332" s="5" t="n">
-        <v>0.01828</v>
-      </c>
-      <c r="F332" s="5" t="n">
-        <v>0.524558</v>
-      </c>
-      <c r="G332" s="5" t="n">
-        <v>4.948449</v>
-      </c>
-      <c r="H332" s="5" t="n">
-        <v>0.19192</v>
-      </c>
-      <c r="I332" s="5" t="n">
-        <v>0.042908</v>
+        <v>1.828e-05</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J332" s="5" t="n">
-        <v>0.288098</v>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="K332" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -35606,15 +35650,19 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Loss on disposition of Mexican subsidiary (note 4)</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -35630,13 +35678,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H333" s="5" t="n">
+        <v>0.002597</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>-0.295968</v>
+        <v>0.01234</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -35692,19 +35738,15 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable (Note 8)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -35720,14 +35762,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H334" s="5" t="n">
-        <v>-0.19124</v>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I334" s="5" t="n">
-        <v>-0.338876</v>
-      </c>
-      <c r="J334" s="5" t="n">
-        <v>-0.288098</v>
+        <v>-0.025</v>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
@@ -35778,42 +35824,34 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F335" s="5" t="n">
+        <v>0.063712</v>
+      </c>
+      <c r="G335" s="5" t="n">
+        <v>0.06486500000000001</v>
       </c>
       <c r="H335" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.039697</v>
       </c>
       <c r="I335" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.02493</v>
       </c>
       <c r="J335" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.015884</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
@@ -35864,38 +35902,36 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>common shares –</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>common shares – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="F336" s="5" t="n">
+        <v>0.524558</v>
+      </c>
+      <c r="G336" s="5" t="n">
+        <v>4.948449</v>
       </c>
       <c r="H336" s="5" t="n">
-        <v>4.592957</v>
+        <v>0.19192</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>4.592957</v>
+        <v>0.042908</v>
       </c>
       <c r="J336" s="5" t="n">
-        <v>6.356388</v>
+        <v>0.288098</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
@@ -35946,12 +35982,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Professional dues</t>
+          <t>Loss on disposition of Mexican subsidiary (note 4)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -35960,17 +35996,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F337" s="5" t="n">
-        <v>0.006337</v>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>0.0063</v>
-      </c>
-      <c r="H337" s="5" t="n">
-        <v>0.018397</v>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I337" s="5" t="n">
-        <v>0.008976</v>
+        <v>-0.295968</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -36026,15 +36068,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Property Investigation</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -36051,17 +36097,13 @@
         </is>
       </c>
       <c r="H338" s="5" t="n">
-        <v>0.01535</v>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.19124</v>
+      </c>
+      <c r="I338" s="5" t="n">
+        <v>-0.338876</v>
+      </c>
+      <c r="J338" s="5" t="n">
+        <v>-0.288098</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
@@ -36112,15 +36154,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Provision for recoverable VAT</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -36137,17 +36183,13 @@
         </is>
       </c>
       <c r="H339" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="J339" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
@@ -36198,12 +36240,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>common shares –</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable (Note 7)</t>
+          <t>common shares – basic and diluted</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -36223,15 +36265,13 @@
         </is>
       </c>
       <c r="H340" s="5" t="n">
-        <v>-0.013</v>
+        <v>4.592957</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.592957</v>
+      </c>
+      <c r="J340" s="5" t="n">
+        <v>6.356388</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
@@ -36287,7 +36327,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Professional dues</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -36297,18 +36337,16 @@
         </is>
       </c>
       <c r="F341" s="5" t="n">
-        <v>0.053283</v>
+        <v>0.006337</v>
       </c>
       <c r="G341" s="5" t="n">
-        <v>0.072449</v>
+        <v>0.0063</v>
       </c>
       <c r="H341" s="5" t="n">
-        <v>0.034197</v>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018397</v>
+      </c>
+      <c r="I341" s="5" t="n">
+        <v>0.008976</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -36369,7 +36407,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Write-down of resource property</t>
+          <t>Property Investigation</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -36389,7 +36427,7 @@
         </is>
       </c>
       <c r="H342" s="5" t="n">
-        <v>-0.016298</v>
+        <v>0.01535</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -36450,12 +36488,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Loss on disposition of Mexican subsidiary</t>
+          <t>Provision for recoverable VAT</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -36474,13 +36512,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I343" s="5" t="n">
-        <v>-0.295968</v>
+      <c r="H343" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -36536,19 +36574,15 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable (Note 7)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -36565,12 +36599,10 @@
         </is>
       </c>
       <c r="H344" s="5" t="n">
-        <v>0.00068</v>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.013</v>
+      </c>
+      <c r="I344" s="5" t="n">
+        <v>-0.025</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
@@ -36624,10 +36656,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2014 and December</t>
+          <t>Wages and benefits</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -36636,16 +36672,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F345" s="5" t="n">
+        <v>0.053283</v>
       </c>
       <c r="G345" s="5" t="n">
-        <v>0.002013</v>
+        <v>0.072449</v>
       </c>
       <c r="H345" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.034197</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -36711,27 +36745,27 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Write-down of resource property</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F346" s="5" t="n">
-        <v>0.004992</v>
-      </c>
-      <c r="G346" s="5" t="n">
-        <v>-0.009390000000000001</v>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H346" s="5" t="n">
-        <v>0.002597</v>
+        <v>-0.016298</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -36792,12 +36826,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Loss on disposition of Mexican subsidiary</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -36806,21 +36840,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F347" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G347" s="5" t="n">
-        <v>0.038</v>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I347" s="5" t="n">
+        <v>-0.295968</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -36876,17 +36912,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -36894,16 +36930,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F348" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G348" s="5" t="n">
-        <v>0.0445</v>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" s="5" t="n">
+        <v>0.00068</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -36962,14 +37000,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>For the years ended December 31, 2014 and December</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -36978,14 +37012,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F349" s="5" t="n">
-        <v>0.003369</v>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G349" s="5" t="n">
-        <v>0.022112</v>
+        <v>0.002013</v>
       </c>
       <c r="H349" s="5" t="n">
-        <v>0.01535</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -37051,27 +37087,27 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Recovery of accounts payable</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F350" s="5" t="n">
+        <v>0.004992</v>
+      </c>
+      <c r="G350" s="5" t="n">
+        <v>-0.009390000000000001</v>
       </c>
       <c r="H350" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.002597</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -37137,7 +37173,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Write-down (recovery) of resource properties</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -37146,16 +37182,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F351" s="5" t="n">
+        <v>0.19</v>
       </c>
       <c r="G351" s="5" t="n">
-        <v>4.573327</v>
-      </c>
-      <c r="H351" s="5" t="n">
-        <v>-0.016298</v>
+        <v>0.038</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -37216,30 +37252,34 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
+          <t>Investor relations</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E352" s="5" t="n">
-        <v>-0.01828</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F352" s="5" t="n">
-        <v>-0.517274</v>
+        <v>0.03</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>-4.93356</v>
-      </c>
-      <c r="H352" s="5" t="n">
-        <v>-0.19124</v>
+        <v>0.0445</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -37300,34 +37340,28 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Property investigation</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F353" s="5" t="n">
+        <v>0.003369</v>
       </c>
       <c r="G353" s="5" t="n">
-        <v>-1.08e-06</v>
+        <v>0.022112</v>
       </c>
       <c r="H353" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.01535</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -37388,12 +37422,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares –</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Recovery of accounts payable</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -37407,11 +37441,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G354" s="5" t="n">
-        <v>4.58254</v>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H354" s="5" t="n">
-        <v>4.592957</v>
+        <v>-0.013</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -37470,10 +37506,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2013 and December</t>
+          <t>Write-down (recovery) of resource properties</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -37482,16 +37522,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F355" s="5" t="n">
-        <v>0.002012</v>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G355" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.573327</v>
+      </c>
+      <c r="H355" s="5" t="n">
+        <v>-0.016298</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -37552,32 +37592,30 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Write-down of resource properties</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="n">
+        <v>-0.01828</v>
+      </c>
+      <c r="F356" s="5" t="n">
+        <v>-0.517274</v>
       </c>
       <c r="G356" s="5" t="n">
-        <v>4.573327</v>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.93356</v>
+      </c>
+      <c r="H356" s="5" t="n">
+        <v>-0.19124</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -37643,7 +37681,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
+          <t>Loss per share – Basic and diluted</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -37656,16 +37694,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F357" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G357" s="5" t="n">
-        <v>-1.1e-07</v>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.08e-06</v>
+      </c>
+      <c r="H357" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -37724,28 +37762,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Weighted average outstanding common shares –</t>
+        </is>
+      </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>For the years ended December 31, 2012 and December</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" s="5" t="n">
-        <v>0.002011</v>
-      </c>
-      <c r="F358" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G358" s="5" t="n">
+        <v>4.58254</v>
+      </c>
+      <c r="H358" s="5" t="n">
+        <v>4.592957</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -37804,83 +37846,593 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>For the years ended December 31, 2013 and December</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F359" s="5" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="G359" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Write-down of resource properties</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G360" s="5" t="n">
+        <v>4.573327</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
         <is>
           <t>Other income</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F361" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G361" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>For the years ended December 31, 2012 and December</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" s="5" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
         <is>
           <t>Loss per share - basic and diluted</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E359" s="5" t="n">
+      <c r="E363" s="5" t="n">
         <v>-1.828e-05</v>
       </c>
-      <c r="F359" s="5" t="n">
+      <c r="F363" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="n">
+        <v>-0.01828</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Weighted average outstanding common shares – basic and</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Weighted average outstanding common shares – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
         <is>
           <t>-</t>
         </is>
